--- a/data/trans_orig/P57B_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P57B_R-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con bienestar emocional por debajo del percentil 15 (Bericat) en 2023</t>
+          <t>Población con peor bienestar socioemocional (percentil 15) (Bericat) en 2023 (tasa de respuesta: 98,25%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6734</t>
+          <t>6392</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22130</t>
+          <t>23643</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12913</t>
+          <t>12817</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23786</t>
+          <t>24672</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21274</t>
+          <t>21520</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41352</t>
+          <t>41338</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>288031</t>
+          <t>286518</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>303427</t>
+          <t>303769</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>265849</t>
+          <t>264963</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>276722</t>
+          <t>276818</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>558444</t>
+          <t>558458</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>578522</t>
+          <t>578276</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,41%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11126</t>
+          <t>10958</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30665</t>
+          <t>32628</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25660</t>
+          <t>25947</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44064</t>
+          <t>44702</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>40930</t>
+          <t>41345</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>70091</t>
+          <t>69864</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>479445</t>
+          <t>477482</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>498984</t>
+          <t>499152</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>462866</t>
+          <t>462228</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>481270</t>
+          <t>480983</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>946949</t>
+          <t>947176</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>976110</t>
+          <t>975695</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,93%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24984</t>
+          <t>25272</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44121</t>
+          <t>45466</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42065</t>
+          <t>41768</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>61399</t>
+          <t>60883</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>71734</t>
+          <t>72034</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>99308</t>
+          <t>98740</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,37%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>264875</t>
+          <t>263530</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>284012</t>
+          <t>283724</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>272168</t>
+          <t>272684</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>291502</t>
+          <t>291799</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>81,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>543255</t>
+          <t>543823</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>570829</t>
+          <t>570529</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,79%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13011</t>
+          <t>14474</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>37147</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24169</t>
+          <t>25210</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60481</t>
+          <t>60006</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44844</t>
+          <t>45749</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>85615</t>
+          <t>84012</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,33%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>258649</t>
+          <t>256502</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>280638</t>
+          <t>279175</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>387297</t>
+          <t>387772</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>423609</t>
+          <t>422568</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>655812</t>
+          <t>657415</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>696583</t>
+          <t>695678</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,83%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33235</t>
+          <t>32704</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>51891</t>
+          <t>51974</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>57431</t>
+          <t>57225</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>74942</t>
+          <t>74864</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>95810</t>
+          <t>94666</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>120478</t>
+          <t>120689</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,42%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>125159</t>
+          <t>125076</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>143815</t>
+          <t>144346</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,69%</t>
+          <t>70,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>132169</t>
+          <t>132247</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>149680</t>
+          <t>149886</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>63,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>72,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>263683</t>
+          <t>263472</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>288351</t>
+          <t>289495</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,64%</t>
+          <t>68,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>75,36%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>29814</t>
+          <t>30105</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>48092</t>
+          <t>47999</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>41978</t>
+          <t>41617</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>59574</t>
+          <t>59682</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>76122</t>
+          <t>74897</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>101963</t>
+          <t>101222</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,25%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>220777</t>
+          <t>220870</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>239055</t>
+          <t>238764</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>82,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>197482</t>
+          <t>197374</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>215078</t>
+          <t>215439</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,82%</t>
+          <t>76,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>83,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>423961</t>
+          <t>424702</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>449802</t>
+          <t>451027</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,76%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>33237</t>
+          <t>33299</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>62097</t>
+          <t>62575</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>32441</t>
+          <t>31961</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>93077</t>
+          <t>96236</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>66666</t>
+          <t>65886</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>139609</t>
+          <t>141549</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,66%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>558931</t>
+          <t>558453</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>587791</t>
+          <t>587729</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>750559</t>
+          <t>747400</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>811195</t>
+          <t>811675</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1325055</t>
+          <t>1323115</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1397998</t>
+          <t>1398778</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,5%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>48473</t>
+          <t>48730</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>160329</t>
+          <t>161663</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>139269</t>
+          <t>140549</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>176432</t>
+          <t>175731</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>163590</t>
+          <t>148455</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>326743</t>
+          <t>325791</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,83%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>766361</t>
+          <t>765027</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>878217</t>
+          <t>877960</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>540162</t>
+          <t>540863</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>577325</t>
+          <t>576045</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>75,48%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1316541</t>
+          <t>1317493</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1479694</t>
+          <t>1494829</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>80,12%</t>
+          <t>80,17%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>90,97%</t>
         </is>
       </c>
     </row>
@@ -3474,12 +3474,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>254253</t>
+          <t>254826</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>365385</t>
+          <t>366914</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>397967</t>
+          <t>397866</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>539590</t>
+          <t>534397</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>691136</t>
+          <t>704388</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>875819</t>
+          <t>881414</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,56%</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3051168</t>
+          <t>3049639</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3162300</t>
+          <t>3161727</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3062715</t>
+          <t>3067908</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3204338</t>
+          <t>3204439</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6143039</t>
+          <t>6137444</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6327722</t>
+          <t>6314470</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>89,96%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P57B_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P57B_R-Provincia-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>12375</t>
+          <t>11601</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6392</t>
+          <t>5999</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23643</t>
+          <t>19714</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>17883</t>
+          <t>19895</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12817</t>
+          <t>14847</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24672</t>
+          <t>26907</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>30258</t>
+          <t>31496</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21520</t>
+          <t>23641</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41338</t>
+          <t>41755</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,59%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>297786</t>
+          <t>306166</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>286518</t>
+          <t>298053</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>303769</t>
+          <t>311768</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>271752</t>
+          <t>296166</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>264963</t>
+          <t>289154</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>276818</t>
+          <t>301214</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>569538</t>
+          <t>602332</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>558458</t>
+          <t>592073</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>578276</t>
+          <t>610187</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,27%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>310161</t>
+          <t>317767</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>310161</t>
+          <t>317767</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>310161</t>
+          <t>317767</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>599796</t>
+          <t>633828</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>599796</t>
+          <t>633828</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>599796</t>
+          <t>633828</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19054</t>
+          <t>19309</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10958</t>
+          <t>11660</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32628</t>
+          <t>32168</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>34249</t>
+          <t>35250</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25947</t>
+          <t>26705</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44702</t>
+          <t>45718</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>53303</t>
+          <t>54559</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>41345</t>
+          <t>42115</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>69864</t>
+          <t>69295</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>491056</t>
+          <t>503569</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>477482</t>
+          <t>490710</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>499152</t>
+          <t>511218</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>472681</t>
+          <t>502925</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>462228</t>
+          <t>492457</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>480983</t>
+          <t>511470</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>963737</t>
+          <t>1006494</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>947176</t>
+          <t>991758</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>975695</t>
+          <t>1018938</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>96,03%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>510110</t>
+          <t>522878</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>510110</t>
+          <t>522878</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>510110</t>
+          <t>522878</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>506930</t>
+          <t>538175</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>506930</t>
+          <t>538175</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>506930</t>
+          <t>538175</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1017040</t>
+          <t>1061053</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1017040</t>
+          <t>1061053</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1017040</t>
+          <t>1061053</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>33482</t>
+          <t>34561</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25272</t>
+          <t>25446</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45466</t>
+          <t>44569</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>50964</t>
+          <t>53308</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>41768</t>
+          <t>43549</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60883</t>
+          <t>63956</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>84446</t>
+          <t>87869</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>72034</t>
+          <t>73384</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>98740</t>
+          <t>101021</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,5%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>275514</t>
+          <t>274798</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>263530</t>
+          <t>264790</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>283724</t>
+          <t>283913</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>282603</t>
+          <t>289219</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>272684</t>
+          <t>278571</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>291799</t>
+          <t>298978</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>81,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>558117</t>
+          <t>564016</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>543823</t>
+          <t>550864</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>570529</t>
+          <t>578501</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>88,74%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>308996</t>
+          <t>309359</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>308996</t>
+          <t>309359</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>308996</t>
+          <t>309359</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>333567</t>
+          <t>342527</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>333567</t>
+          <t>342527</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>333567</t>
+          <t>342527</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>642563</t>
+          <t>651885</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>642563</t>
+          <t>651885</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>642563</t>
+          <t>651885</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>22001</t>
+          <t>23447</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14474</t>
+          <t>13858</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37147</t>
+          <t>36374</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>44205</t>
+          <t>47838</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25210</t>
+          <t>37049</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60006</t>
+          <t>60723</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>66206</t>
+          <t>71286</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45749</t>
+          <t>56204</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>84012</t>
+          <t>89731</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>12,16%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>271648</t>
+          <t>324241</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>256502</t>
+          <t>311314</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>279175</t>
+          <t>333830</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>403573</t>
+          <t>342613</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>387772</t>
+          <t>329728</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>422568</t>
+          <t>353402</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>675221</t>
+          <t>666853</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>657415</t>
+          <t>648408</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>695678</t>
+          <t>681935</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>92,39%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>293649</t>
+          <t>347688</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>293649</t>
+          <t>347688</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>293649</t>
+          <t>347688</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>447778</t>
+          <t>390451</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>447778</t>
+          <t>390451</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>447778</t>
+          <t>390451</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>741427</t>
+          <t>738139</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>741427</t>
+          <t>738139</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>741427</t>
+          <t>738139</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>41872</t>
+          <t>48177</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32704</t>
+          <t>38257</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>51974</t>
+          <t>58682</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>65984</t>
+          <t>70688</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>57225</t>
+          <t>61749</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>74864</t>
+          <t>80479</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>107856</t>
+          <t>118864</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>94666</t>
+          <t>105956</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>120689</t>
+          <t>133350</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,04%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>135178</t>
+          <t>155775</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>125076</t>
+          <t>145270</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>144346</t>
+          <t>165695</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>76,38%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>71,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>141127</t>
+          <t>154926</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>132247</t>
+          <t>145135</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>149886</t>
+          <t>163865</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>68,67%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,85%</t>
+          <t>64,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>72,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>276305</t>
+          <t>310702</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>263472</t>
+          <t>296216</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>289495</t>
+          <t>323610</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>72,33%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>68,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>75,33%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>177050</t>
+          <t>203952</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>177050</t>
+          <t>203952</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>177050</t>
+          <t>203952</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>207111</t>
+          <t>225614</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>207111</t>
+          <t>225614</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>207111</t>
+          <t>225614</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>384161</t>
+          <t>429566</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>384161</t>
+          <t>429566</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>384161</t>
+          <t>429566</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>37932</t>
+          <t>40205</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>30105</t>
+          <t>31598</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>47999</t>
+          <t>50305</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>50331</t>
+          <t>52546</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>41617</t>
+          <t>43656</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>59682</t>
+          <t>62279</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>88263</t>
+          <t>92751</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>74897</t>
+          <t>79361</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>101222</t>
+          <t>105836</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,83%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>230937</t>
+          <t>229749</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>220870</t>
+          <t>219649</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>238764</t>
+          <t>238356</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>206725</t>
+          <t>211204</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>197374</t>
+          <t>201471</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>215439</t>
+          <t>220094</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>80,08%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>437661</t>
+          <t>440953</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>424702</t>
+          <t>427868</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>451027</t>
+          <t>454343</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>80,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>85,13%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>268869</t>
+          <t>269954</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>268869</t>
+          <t>269954</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>268869</t>
+          <t>269954</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>525924</t>
+          <t>533704</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>525924</t>
+          <t>533704</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>525924</t>
+          <t>533704</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>44724</t>
+          <t>51139</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>33299</t>
+          <t>37778</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>62575</t>
+          <t>69073</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>66634</t>
+          <t>79413</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>31961</t>
+          <t>63537</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>96236</t>
+          <t>96730</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>111358</t>
+          <t>130552</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>65886</t>
+          <t>109860</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>141549</t>
+          <t>155646</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>10,52%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>576304</t>
+          <t>664969</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>558453</t>
+          <t>647035</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>587729</t>
+          <t>678330</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>777002</t>
+          <t>684601</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>747400</t>
+          <t>667284</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>811675</t>
+          <t>700477</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1353306</t>
+          <t>1349570</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1323115</t>
+          <t>1324476</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1398778</t>
+          <t>1370262</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>92,58%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>621028</t>
+          <t>716108</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>621028</t>
+          <t>716108</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>621028</t>
+          <t>716108</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>843636</t>
+          <t>764014</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>843636</t>
+          <t>764014</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>843636</t>
+          <t>764014</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1464664</t>
+          <t>1480122</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1464664</t>
+          <t>1480122</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1464664</t>
+          <t>1480122</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>112189</t>
+          <t>127472</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>48730</t>
+          <t>108689</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>161663</t>
+          <t>149843</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>157232</t>
+          <t>182594</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>140549</t>
+          <t>162124</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>175731</t>
+          <t>202635</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>269421</t>
+          <t>310066</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>148455</t>
+          <t>281836</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>325791</t>
+          <t>340605</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>20,95%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>814501</t>
+          <t>668324</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>765027</t>
+          <t>645953</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>877960</t>
+          <t>687107</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>81,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>559362</t>
+          <t>647437</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>540863</t>
+          <t>627396</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>576045</t>
+          <t>667907</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>75,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1373863</t>
+          <t>1315761</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1317493</t>
+          <t>1285222</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1494829</t>
+          <t>1343991</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>79,05%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>82,67%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>926690</t>
+          <t>795796</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>926690</t>
+          <t>795796</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>926690</t>
+          <t>795796</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>716594</t>
+          <t>830031</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>716594</t>
+          <t>830031</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>716594</t>
+          <t>830031</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1643284</t>
+          <t>1625827</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1643284</t>
+          <t>1625827</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1643284</t>
+          <t>1625827</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3469,32 +3469,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>323628</t>
+          <t>355911</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>254826</t>
+          <t>321937</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>366914</t>
+          <t>393887</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,32 +3504,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>487482</t>
+          <t>541532</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>397866</t>
+          <t>505520</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>534397</t>
+          <t>575781</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>811110</t>
+          <t>897443</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>704388</t>
+          <t>850906</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>881414</t>
+          <t>949298</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>13,27%</t>
         </is>
       </c>
     </row>
@@ -3582,32 +3582,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3092925</t>
+          <t>3127590</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3049639</t>
+          <t>3089614</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3161727</t>
+          <t>3161564</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,32 +3617,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3114823</t>
+          <t>3129091</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3067908</t>
+          <t>3094842</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3204439</t>
+          <t>3165103</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6207748</t>
+          <t>6256681</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6137444</t>
+          <t>6204826</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6314470</t>
+          <t>6303218</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>88,11%</t>
         </is>
       </c>
     </row>
@@ -3695,17 +3695,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3416553</t>
+          <t>3483501</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3416553</t>
+          <t>3483501</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3416553</t>
+          <t>3483501</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3730,17 +3730,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3602305</t>
+          <t>3670623</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3602305</t>
+          <t>3670623</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3602305</t>
+          <t>3670623</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7018858</t>
+          <t>7154124</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7018858</t>
+          <t>7154124</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7018858</t>
+          <t>7154124</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
